--- a/reports/pdf_change_20260812.xlsx
+++ b/reports/pdf_change_20260812.xlsx
@@ -38,11 +38,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="11"/>
     </font>
@@ -67,6 +62,11 @@
       <i val="1"/>
       <color rgb="00808080"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -74,11 +74,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -103,6 +98,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E4ECF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -132,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -143,19 +143,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,17 +170,12 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -540,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -566,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 2/7  ·  대기: KoAct, KoAct, TIME, TIME, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,738억   ·   현금 133억(2.8%)      당일 2026-08-12  vs  전영업일 2026-08-11      매수 4종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -587,377 +588,933 @@
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
     </row>
-    <row r="5" ht="19" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-    </row>
-    <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-    </row>
-    <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-    </row>
-    <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>하림지주  (신규)</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>123</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>1469918880</v>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.32%</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>0→123</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>덕산하이메탈</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>-97</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>-963000480</v>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>1.42%→1.19%</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>645→548</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>서부T&amp;D</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>84</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>987376320</v>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>1.65%→1.92%</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>665→749</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>고영</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>-29</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>-981638400</v>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>0.80%→0.61%</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>112→83</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>하나머티리얼즈</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>1502488800</v>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>1.02%→1.39%</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>75→98</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>-23</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>-1471632000</v>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>0.98%→0.67%</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>71→48</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>에스피지</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>1411776000</v>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>0.55%→0.90%</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>23→35</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>노바렉스</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>-224718000</v>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>0.10%→0.05%</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>26→13</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>-1410537600</v>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>5.65%→5.25%</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>217→205</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n"/>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>한중엔시에스</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>-299692800</v>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>0.68%→0.60%</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>82→74</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="19" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,270억   ·   현금 10억(0.2%)      당일 2026-08-12  vs  전영업일 2026-08-11      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="19" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,676억   ·   현금 32억(1.2%)      당일 2026-08-12  vs  전영업일 2026-08-11      매수 3종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>제주반도체</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>70</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>4454912000</v>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>1.61%→3.32%</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>69→139</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>덕산하이메탈</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>-281</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>-1903066880</v>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>1.30%→0.55%</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>499→218</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>에스피지</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>4012800000</v>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>1.43%→3.01%</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>50→100</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>-148</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>-3490432000</v>
+      </c>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>2.41%→1.33%</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>298→150</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>오킨스전자</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>48</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>534927360</v>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>0.19%→0.41%</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>50→98</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>-122</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>-2430630400</v>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>1.84%→0.89%</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>241→119</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="n"/>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>선익시스템</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v>-992640000</v>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>1.87%→1.49%</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>100→80</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,463억   ·   현금 15억(0.6%)      당일 2026-08-12  vs  전영업일 2026-08-11      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 287억   ·   현금 7억(2.5%)      당일 2026-08-12  vs  전영업일 2026-08-11      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="10" t="n"/>
-      <c r="J12" s="10" t="n"/>
-      <c r="K12" s="10" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="8" t="n"/>
+      <c r="J28" s="8" t="n"/>
+      <c r="K28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G29" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H29" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I29" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J29" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr">
+      <c r="K29" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>에프앤가이드</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B30" s="11" t="n">
         <v>34</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C30" s="11" t="n">
         <v>45478400</v>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>3.08%→3.25%</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>646→680</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G30" s="14" t="inlineStr">
         <is>
           <t>상신이디피</t>
         </is>
       </c>
-      <c r="H14" s="17" t="n">
+      <c r="H30" s="15" t="n">
         <v>-38</v>
       </c>
-      <c r="I14" s="17" t="n">
+      <c r="I30" s="15" t="n">
         <v>-51637440</v>
       </c>
-      <c r="J14" s="18" t="inlineStr">
+      <c r="J30" s="16" t="inlineStr">
         <is>
           <t>1.56%→1.38%</t>
         </is>
       </c>
-      <c r="K14" s="15" t="inlineStr">
+      <c r="K30" s="13" t="inlineStr">
         <is>
           <t>322→284</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>코스맥스엔비티</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B31" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C31" s="11" t="n">
         <v>15450800</v>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>0.05%→0.10%</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>17→36</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G31" s="14" t="inlineStr">
         <is>
           <t>원익머트리얼즈</t>
         </is>
       </c>
-      <c r="H15" s="17" t="n">
+      <c r="H31" s="15" t="n">
         <v>-18</v>
       </c>
-      <c r="I15" s="17" t="n">
+      <c r="I31" s="15" t="n">
         <v>-48632400</v>
       </c>
-      <c r="J15" s="18" t="inlineStr">
+      <c r="J31" s="16" t="inlineStr">
         <is>
           <t>2.59%→2.42%</t>
         </is>
       </c>
-      <c r="K15" s="15" t="inlineStr">
+      <c r="K31" s="13" t="inlineStr">
         <is>
           <t>269→251</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>피에스케이</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B32" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C32" s="11" t="n">
         <v>60511200</v>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>2.95%→3.17%</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>82→88</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G32" s="14" t="inlineStr">
         <is>
           <t>솔브레인홀딩스</t>
         </is>
       </c>
-      <c r="H16" s="17" t="n">
+      <c r="H32" s="15" t="n">
         <v>-13</v>
       </c>
-      <c r="I16" s="17" t="n">
+      <c r="I32" s="15" t="n">
         <v>-38087400</v>
       </c>
-      <c r="J16" s="18" t="inlineStr">
+      <c r="J32" s="16" t="inlineStr">
         <is>
           <t>0.72%→0.59%</t>
         </is>
       </c>
-      <c r="K16" s="15" t="inlineStr">
+      <c r="K32" s="13" t="inlineStr">
         <is>
           <t>69→56</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>실리콘투</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B33" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C33" s="11" t="n">
         <v>11673600</v>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>0.76%→0.80%</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>73→77</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G33" s="14" t="inlineStr">
         <is>
           <t>HK이노엔</t>
         </is>
       </c>
-      <c r="H17" s="17" t="n">
+      <c r="H33" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I17" s="17" t="n">
+      <c r="I33" s="15" t="n">
         <v>-22610000</v>
       </c>
-      <c r="J17" s="18" t="inlineStr">
+      <c r="J33" s="16" t="inlineStr">
         <is>
           <t>0.13%→0.05%</t>
         </is>
       </c>
-      <c r="K17" s="15" t="inlineStr">
+      <c r="K33" s="13" t="inlineStr">
         <is>
           <t>11→4</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 621억   ·   현금 10억(1.6%)      당일 2026-08-12  vs  전영업일 2026-08-11      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="4" t="n"/>
+      <c r="J35" s="4" t="n"/>
+      <c r="K35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="38" ht="19" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
-      <c r="J22" s="4" t="n"/>
-      <c r="K22" s="4" t="n"/>
+      <c r="B38" s="20" t="n"/>
+      <c r="C38" s="20" t="n"/>
+      <c r="D38" s="20" t="n"/>
+      <c r="E38" s="20" t="n"/>
+      <c r="F38" s="20" t="n"/>
+      <c r="G38" s="20" t="n"/>
+      <c r="H38" s="20" t="n"/>
+      <c r="I38" s="20" t="n"/>
+      <c r="J38" s="20" t="n"/>
+      <c r="K38" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A22:K22"/>
-    <mergeCell ref="A12:E12"/>
+  <mergeCells count="18">
+    <mergeCell ref="G17:K17"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A35:K35"/>
+    <mergeCell ref="A17:E17"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="G12:K12"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A24:K24"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A19:K19"/>
-    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="G28:K28"/>
+    <mergeCell ref="A38:K38"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="A14:K14"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20260812.xlsx
+++ b/reports/pdf_change_20260812.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,738억   ·   현금 133억(2.8%)      당일 2026-08-12  vs  전영업일 2026-08-11      매수 4종목  /  매도 6종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,732억   ·   현금 133억(2.8%)      당일 2026-08-12  vs  전영업일 2026-08-11      매수 4종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>123</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1469918880</v>
+        <v>1472767560</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-97</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-963000480</v>
+        <v>-964866760</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>84</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>987376320</v>
+        <v>989289840</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-29</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-981638400</v>
+        <v>-983540800</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>23</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1502488800</v>
+        <v>1505400600</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-23</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1471632000</v>
+        <v>-1474484000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1411776000</v>
+        <v>1414512000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-13</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-224718000</v>
+        <v>-225153500</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>-12</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1410537600</v>
+        <v>-1413271200</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>-8</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-299692800</v>
+        <v>-300273600</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,270억   ·   현금 10억(0.2%)      당일 2026-08-12  vs  전영업일 2026-08-11      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,183억   ·   현금 10억(0.2%)      당일 2026-08-12  vs  전영업일 2026-08-11      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -919,7 +919,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,676억   ·   현금 32억(1.2%)      당일 2026-08-12  vs  전영업일 2026-08-11      매수 3종목  /  매도 4종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,694억   ·   현금 32억(1.2%)      당일 2026-08-12  vs  전영업일 2026-08-11      매수 3종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -1015,7 +1015,7 @@
         <v>70</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>4454912000</v>
+        <v>4442256000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>-281</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-1903066880</v>
+        <v>-1897660440</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>50</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>4012800000</v>
+        <v>4001400000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>-148</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-3490432000</v>
+        <v>-3480516000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>48</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>534927360</v>
+        <v>533407680</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>-122</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-2430630400</v>
+        <v>-2423725200</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>-20</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-992640000</v>
+        <v>-989820000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,463억   ·   현금 15억(0.6%)      당일 2026-08-12  vs  전영업일 2026-08-11      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,418억   ·   현금 15억(0.6%)      당일 2026-08-12  vs  전영업일 2026-08-11      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1192,7 +1192,7 @@
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 287억   ·   현금 7억(2.5%)      당일 2026-08-12  vs  전영업일 2026-08-11      매수 4종목  /  매도 4종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 291억   ·   현금 7억(2.4%)      당일 2026-08-12  vs  전영업일 2026-08-11      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
@@ -1288,11 +1288,11 @@
         <v>34</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>45478400</v>
+        <v>46460320</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>3.08%→3.25%</t>
+          <t>3.10%→3.27%</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
@@ -1309,11 +1309,11 @@
         <v>-38</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-51637440</v>
+        <v>-52243920</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>1.56%→1.38%</t>
+          <t>1.56%→1.37%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
@@ -1332,7 +1332,7 @@
         <v>19</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>15450800</v>
+        <v>15046480</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1353,11 +1353,11 @@
         <v>-18</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-48632400</v>
+        <v>-49795200</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>2.59%→2.42%</t>
+          <t>2.62%→2.44%</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
@@ -1376,11 +1376,11 @@
         <v>6</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>60511200</v>
+        <v>58869600</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>2.95%→3.17%</t>
+          <t>2.83%→3.04%</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -1397,11 +1397,11 @@
         <v>-13</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-38087400</v>
+        <v>-40261000</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>0.72%→0.59%</t>
+          <t>0.75%→0.61%</t>
         </is>
       </c>
       <c r="K32" s="13" t="inlineStr">
@@ -1420,11 +1420,11 @@
         <v>4</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>11673600</v>
+        <v>12175200</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>0.76%→0.80%</t>
+          <t>0.78%→0.82%</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
@@ -1441,11 +1441,11 @@
         <v>-7</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-22610000</v>
+        <v>-22477000</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>0.13%→0.05%</t>
+          <t>0.12%→0.05%</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
@@ -1457,7 +1457,7 @@
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 621억   ·   현금 10억(1.6%)      당일 2026-08-12  vs  전영업일 2026-08-11      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 615억   ·   현금 10억(1.6%)      당일 2026-08-12  vs  전영업일 2026-08-11      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B35" s="4" t="n"/>
